--- a/artfynd/A 44262-2022 artfynd.xlsx
+++ b/artfynd/A 44262-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44262-2022 artfynd.xlsx
+++ b/artfynd/A 44262-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>406091</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577120.6819896156</v>
+        <v>577121</v>
       </c>
       <c r="R2" t="n">
-        <v>6555520.734232211</v>
+        <v>6555521</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>2012-04-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-04-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,16 +784,11 @@
         <v>406092</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577149.2724093721</v>
+        <v>577149</v>
       </c>
       <c r="R3" t="n">
-        <v>6555531.065432675</v>
+        <v>6555531</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,19 +853,9 @@
           <t>2012-04-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-04-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +884,127 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104067198</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fjellskäftereservatet nr 94, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577090</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6555507</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>fridlyst</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog m inslag av löv</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44262-2022 artfynd.xlsx
+++ b/artfynd/A 44262-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406091</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406092</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,8 +1020,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104067198</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>